--- a/詳細設計図/ログアウト機能_詳細設計図.xlsx
+++ b/詳細設計図/ログアウト機能_詳細設計図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\プロジェクト演習\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76565B30-3DC3-484D-9C56-6EE86423A94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F984A8D-397D-46B9-91C8-CAEF91E1D81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,20 +315,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>Alt-1:セッションがない場合
-1:「ログアウト済です」と表示</t>
-    <rPh sb="14" eb="16">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>スミ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>①ユーザーはメニュー画面から[ログアウト]ボタンを押下
 ②システムはセッションを破棄(Alt-1)
 ③システムはログアウト画面へ遷移
@@ -367,6 +353,20 @@
     </rPh>
     <rPh sb="131" eb="133">
       <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Alt-1:セッションがない場合
+1:logout.jspに「ログアウト済です」と表示</t>
+    <rPh sb="14" eb="16">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>スミ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1411,6 +1411,96 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1426,99 +1516,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1540,6 +1540,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1558,18 +1564,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1591,38 +1591,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3123,19 +3123,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3147,70 +3147,70 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
+      <c r="A2" s="62"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="52">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="81">
         <v>45705</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="56"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="77" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="78"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="67" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="79" t="s">
+      <c r="D6" s="52" t="s">
         <v>72</v>
       </c>
       <c r="E6" s="39"/>
@@ -3218,15 +3218,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="60"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="67" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="79" t="s">
+      <c r="D7" s="52" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="39"/>
@@ -3234,15 +3234,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="60"/>
+      <c r="J7" s="53"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="67" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="79" t="s">
+      <c r="D8" s="52" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="39"/>
@@ -3250,63 +3250,63 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="60"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="71" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="56"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="69"/>
+      <c r="B10" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="54" t="s">
         <v>83</v>
-      </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="81"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="59" t="s">
-        <v>82</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="60"/>
+      <c r="J10" s="53"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="57" t="s">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="59"/>
+      <c r="D11" s="54"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="60"/>
+      <c r="J11" s="53"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="67" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="54" t="s">
         <v>81</v>
       </c>
       <c r="E12" s="39"/>
@@ -3314,21 +3314,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="60"/>
+      <c r="J12" s="53"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="61" t="s">
+      <c r="A13" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="62"/>
-      <c r="C13" s="63"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="76"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="48"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4319,6 +4319,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4327,25 +4346,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4367,16 +4367,16 @@
       <c r="A1" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4388,28 +4388,28 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
+      <c r="A2" s="62"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="55"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="85"/>
@@ -5780,16 +5780,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5801,34 +5801,34 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
+      <c r="A2" s="62"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="52">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="81">
         <v>45708</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="85"/>
@@ -7194,16 +7194,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="46" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="47"/>
+      <c r="G1" s="77"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7215,65 +7215,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
+      <c r="A2" s="62"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="52">
+      <c r="E2" s="79"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="81">
         <v>45708</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="55"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="56"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="75"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="67"/>
+      <c r="A4" s="62"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="56"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="75"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="92"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="97" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="97"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="96" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="39"/>
@@ -7284,7 +7284,7 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="98"/>
+      <c r="J6" s="89"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="99"/>
@@ -7299,7 +7299,7 @@
       <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="67"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7311,7 +7311,7 @@
       <c r="J8" s="102"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="67"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7323,7 +7323,7 @@
       <c r="J9" s="102"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="67"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7335,7 +7335,7 @@
       <c r="J10" s="102"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="67"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7347,7 +7347,7 @@
       <c r="J11" s="102"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="67"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7359,7 +7359,7 @@
       <c r="J12" s="102"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="67"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7371,7 +7371,7 @@
       <c r="J13" s="102"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="96" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="39"/>
@@ -7382,15 +7382,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="98"/>
+      <c r="J14" s="89"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="96" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="79" t="s">
+      <c r="D15" s="52" t="s">
         <v>74</v>
       </c>
       <c r="E15" s="39"/>
@@ -7405,7 +7405,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="94" t="s">
+      <c r="A16" s="96" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="39"/>
@@ -7426,10 +7426,10 @@
         <v>19</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="98"/>
+      <c r="J16" s="89"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="90" t="s">
         <v>76</v>
       </c>
       <c r="B17" s="39"/>
@@ -7442,82 +7442,82 @@
       <c r="G17" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="79" t="s">
+      <c r="H17" s="52" t="s">
         <v>79</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="98"/>
+      <c r="J17" s="89"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="95"/>
+      <c r="A18" s="90"/>
       <c r="B18" s="39"/>
       <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="79"/>
+      <c r="H18" s="52"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="98"/>
+      <c r="J18" s="89"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="95"/>
+      <c r="A19" s="90"/>
       <c r="B19" s="39"/>
       <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="79"/>
+      <c r="H19" s="52"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="98"/>
+      <c r="J19" s="89"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="95"/>
+      <c r="A20" s="90"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="79"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="98"/>
+      <c r="J20" s="89"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="95"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="79"/>
+      <c r="H21" s="52"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="98"/>
+      <c r="J21" s="89"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="95"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="79"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="98"/>
+      <c r="J22" s="89"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="91"/>
-      <c r="B23" s="92"/>
-      <c r="C23" s="93"/>
+      <c r="A23" s="93"/>
+      <c r="B23" s="94"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="104"/>
-      <c r="I23" s="92"/>
+      <c r="I23" s="94"/>
       <c r="J23" s="105"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8499,16 +8499,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8525,11 +8520,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8549,81 +8549,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="46" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="46" t="s">
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="46" t="s">
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="77"/>
+      <c r="Q1" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="77"/>
+      <c r="S1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="97"/>
+      <c r="T1" s="98"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="67"/>
+      <c r="A2" s="62"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="48"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="78"/>
       <c r="H2" s="100"/>
       <c r="I2" s="100"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="48"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="78"/>
       <c r="L2" s="100"/>
       <c r="M2" s="100"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="48"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="48"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="78"/>
       <c r="T2" s="101"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="67"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="50"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="80"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="50"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="80"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="50"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="80"/>
       <c r="T3" s="102"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
@@ -8646,36 +8646,36 @@
       <c r="Q4" s="88"/>
       <c r="R4" s="87"/>
       <c r="S4" s="88"/>
-      <c r="T4" s="110"/>
+      <c r="T4" s="115"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="111" t="s">
+      <c r="B5" s="92"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
-      <c r="S5" s="90"/>
-      <c r="T5" s="97"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="92"/>
+      <c r="M5" s="92"/>
+      <c r="N5" s="92"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="92"/>
+      <c r="Q5" s="92"/>
+      <c r="R5" s="92"/>
+      <c r="S5" s="92"/>
+      <c r="T5" s="98"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="96" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="39"/>
@@ -8683,7 +8683,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="52" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="39"/>
@@ -8698,10 +8698,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="98"/>
+      <c r="T6" s="89"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="96" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="39"/>
@@ -8709,7 +8709,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="79" t="s">
+      <c r="G7" s="52" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="39"/>
@@ -8724,7 +8724,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="98"/>
+      <c r="T7" s="89"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8923,7 +8923,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="96" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="40"/>
@@ -8965,33 +8965,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="112">
+      <c r="A16" s="106">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="113" t="s">
+      <c r="C16" s="107" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="113" t="s">
+      <c r="E16" s="107" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="106" t="s">
+      <c r="G16" s="113" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="113" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="40"/>
-      <c r="L16" s="108" t="s">
+      <c r="L16" s="110" t="s">
         <v>58</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="108" t="s">
+      <c r="O16" s="110" t="s">
         <v>59</v>
       </c>
       <c r="P16" s="39"/>
@@ -9007,33 +9007,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="112">
+      <c r="A17" s="106">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="113" t="s">
+      <c r="C17" s="107" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="113" t="s">
+      <c r="E17" s="107" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="106" t="s">
+      <c r="G17" s="113" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="106" t="s">
+      <c r="J17" s="113" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="40"/>
-      <c r="L17" s="108" t="s">
+      <c r="L17" s="110" t="s">
         <v>64</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="108" t="s">
+      <c r="O17" s="110" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="39"/>
@@ -9049,23 +9049,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="112"/>
+      <c r="A18" s="106"/>
       <c r="B18" s="40"/>
-      <c r="C18" s="113"/>
+      <c r="C18" s="107"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="113"/>
+      <c r="E18" s="107"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="106" t="s">
+      <c r="G18" s="113" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="106"/>
+      <c r="J18" s="113"/>
       <c r="K18" s="40"/>
-      <c r="L18" s="108"/>
+      <c r="L18" s="110"/>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="108"/>
+      <c r="O18" s="110"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
@@ -9079,23 +9079,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="112"/>
+      <c r="A19" s="106"/>
       <c r="B19" s="40"/>
-      <c r="C19" s="113"/>
+      <c r="C19" s="107"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="113"/>
+      <c r="E19" s="107"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="106" t="s">
+      <c r="G19" s="113" t="s">
         <v>70</v>
       </c>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="106"/>
+      <c r="J19" s="113"/>
       <c r="K19" s="40"/>
-      <c r="L19" s="108"/>
+      <c r="L19" s="110"/>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="108"/>
+      <c r="O19" s="110"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
@@ -9109,21 +9109,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="112"/>
+      <c r="A20" s="106"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="113"/>
+      <c r="C20" s="107"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="113"/>
+      <c r="E20" s="107"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="106"/>
+      <c r="G20" s="113"/>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="106"/>
+      <c r="J20" s="113"/>
       <c r="K20" s="40"/>
-      <c r="L20" s="108"/>
+      <c r="L20" s="110"/>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="108"/>
+      <c r="O20" s="110"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
@@ -9137,21 +9137,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="112"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="113"/>
+      <c r="C21" s="107"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="113"/>
+      <c r="E21" s="107"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="106"/>
+      <c r="G21" s="113"/>
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="106"/>
+      <c r="J21" s="113"/>
       <c r="K21" s="40"/>
-      <c r="L21" s="108"/>
+      <c r="L21" s="110"/>
       <c r="M21" s="39"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="108"/>
+      <c r="O21" s="110"/>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
@@ -9165,21 +9165,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="112"/>
+      <c r="A22" s="106"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="113"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="113"/>
+      <c r="E22" s="107"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="106"/>
+      <c r="G22" s="113"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="106"/>
+      <c r="J22" s="113"/>
       <c r="K22" s="40"/>
-      <c r="L22" s="108"/>
+      <c r="L22" s="110"/>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="108"/>
+      <c r="O22" s="110"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
@@ -9193,21 +9193,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="112"/>
+      <c r="A23" s="106"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="113"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="113"/>
+      <c r="E23" s="107"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="106"/>
+      <c r="G23" s="113"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="106"/>
+      <c r="J23" s="113"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="108"/>
+      <c r="L23" s="110"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="108"/>
+      <c r="O23" s="110"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9221,21 +9221,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="112"/>
+      <c r="A24" s="106"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="113"/>
+      <c r="C24" s="107"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="113"/>
+      <c r="E24" s="107"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="106"/>
+      <c r="G24" s="113"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="106"/>
+      <c r="J24" s="113"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="108"/>
+      <c r="L24" s="110"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="108"/>
+      <c r="O24" s="110"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9249,21 +9249,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="112"/>
+      <c r="A25" s="106"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="113"/>
+      <c r="C25" s="107"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="113"/>
+      <c r="E25" s="107"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="106"/>
+      <c r="G25" s="113"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="106"/>
+      <c r="J25" s="113"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="108"/>
+      <c r="L25" s="110"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="108"/>
+      <c r="O25" s="110"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9277,21 +9277,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="112"/>
+      <c r="A26" s="106"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="113"/>
+      <c r="C26" s="107"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="113"/>
+      <c r="E26" s="107"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="106"/>
+      <c r="G26" s="113"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="106"/>
+      <c r="J26" s="113"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="108"/>
+      <c r="L26" s="110"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="108"/>
+      <c r="O26" s="110"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9305,21 +9305,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="112"/>
+      <c r="A27" s="106"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="113"/>
+      <c r="C27" s="107"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="113"/>
+      <c r="E27" s="107"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="106"/>
+      <c r="G27" s="113"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="106"/>
+      <c r="J27" s="113"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="108"/>
+      <c r="L27" s="110"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="108"/>
+      <c r="O27" s="110"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9333,21 +9333,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="112"/>
+      <c r="A28" s="106"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="113"/>
+      <c r="C28" s="107"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="113"/>
+      <c r="E28" s="107"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="106"/>
+      <c r="G28" s="113"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="106"/>
+      <c r="J28" s="113"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="108"/>
+      <c r="L28" s="110"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="108"/>
+      <c r="O28" s="110"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9361,21 +9361,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="112"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="113"/>
+      <c r="C29" s="107"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="113"/>
+      <c r="E29" s="107"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="106"/>
+      <c r="G29" s="113"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="106"/>
+      <c r="J29" s="113"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="108"/>
+      <c r="L29" s="110"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="108"/>
+      <c r="O29" s="110"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9389,21 +9389,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="112"/>
+      <c r="A30" s="106"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="113"/>
+      <c r="C30" s="107"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="113"/>
+      <c r="E30" s="107"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="106"/>
+      <c r="G30" s="113"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="106"/>
+      <c r="J30" s="113"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="108"/>
+      <c r="L30" s="110"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="108"/>
+      <c r="O30" s="110"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9417,23 +9417,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="115"/>
-      <c r="B31" s="93"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="92"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="109"/>
-      <c r="M31" s="92"/>
-      <c r="N31" s="93"/>
-      <c r="O31" s="109"/>
-      <c r="P31" s="92"/>
-      <c r="Q31" s="93"/>
+      <c r="A31" s="108"/>
+      <c r="B31" s="95"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="95"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="95"/>
+      <c r="L31" s="111"/>
+      <c r="M31" s="94"/>
+      <c r="N31" s="95"/>
+      <c r="O31" s="111"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="95"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10431,6 +10431,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10455,118 +10567,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/詳細設計図/ログアウト機能_詳細設計図.xlsx
+++ b/詳細設計図/ログアウト機能_詳細設計図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\プロジェクト演習\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F984A8D-397D-46B9-91C8-CAEF91E1D81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984A66BA-5A8A-4AAD-BD65-4981E0881269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,15 +358,22 @@
   </si>
   <si>
     <t>Alt-1:セッションがない場合
-1:logout.jspに「ログアウト済です」と表示</t>
+1.ログアウト画面へ遷移
+2.ログアウト画面は「ログアウト画面」「ログアウト済です」の文章と[ログイン画面へ]ボタンを表示</t>
     <rPh sb="14" eb="16">
       <t>バアイ</t>
     </rPh>
-    <rPh sb="36" eb="37">
-      <t>スミ</t>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
     </rPh>
-    <rPh sb="41" eb="43">
-      <t>ヒョウジ</t>
+    <rPh sb="27" eb="29">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1411,114 +1418,114 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1540,36 +1547,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1591,38 +1598,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3123,19 +3130,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3147,70 +3154,70 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
+      <c r="A2" s="67"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="81">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="52">
         <v>45705</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="49" t="s">
+      <c r="B5" s="70"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="78"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="58" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="39"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="52" t="s">
+      <c r="D6" s="79" t="s">
         <v>72</v>
       </c>
       <c r="E6" s="39"/>
@@ -3218,15 +3225,15 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="58" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="79" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="39"/>
@@ -3234,15 +3241,15 @@
       <c r="G7" s="39"/>
       <c r="H7" s="39"/>
       <c r="I7" s="39"/>
-      <c r="J7" s="53"/>
+      <c r="J7" s="60"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="58" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="52" t="s">
+      <c r="D8" s="79" t="s">
         <v>73</v>
       </c>
       <c r="E8" s="39"/>
@@ -3250,33 +3257,33 @@
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="53"/>
+      <c r="J8" s="60"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="57" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="40"/>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="81"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71" t="s">
+      <c r="A10" s="73"/>
+      <c r="B10" s="57" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="40"/>
-      <c r="D10" s="54" t="s">
+      <c r="D10" s="59" t="s">
         <v>83</v>
       </c>
       <c r="E10" s="39"/>
@@ -3284,29 +3291,29 @@
       <c r="G10" s="39"/>
       <c r="H10" s="39"/>
       <c r="I10" s="39"/>
-      <c r="J10" s="53"/>
+      <c r="J10" s="60"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="74"/>
+      <c r="B11" s="57" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="40"/>
-      <c r="D11" s="54"/>
+      <c r="D11" s="59"/>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
       <c r="G11" s="39"/>
       <c r="H11" s="39"/>
       <c r="I11" s="39"/>
-      <c r="J11" s="53"/>
+      <c r="J11" s="60"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="58" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="39"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="59" t="s">
         <v>81</v>
       </c>
       <c r="E12" s="39"/>
@@ -3314,21 +3321,21 @@
       <c r="G12" s="39"/>
       <c r="H12" s="39"/>
       <c r="I12" s="39"/>
-      <c r="J12" s="53"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4319,17 +4326,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4338,14 +4342,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4367,16 +4374,16 @@
       <c r="A1" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4388,28 +4395,28 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
+      <c r="A2" s="67"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="74"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="85"/>
@@ -5780,16 +5787,16 @@
       <c r="A1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -5801,34 +5808,34 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
+      <c r="A2" s="67"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="81">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="52">
         <v>45708</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="85"/>
@@ -7194,16 +7201,16 @@
       <c r="A1" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="47"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -7215,65 +7222,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
+      <c r="A2" s="67"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="81">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="52">
         <v>45708</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
+      <c r="A4" s="67"/>
       <c r="B4" s="42"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="75"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="97" t="s">
+      <c r="B5" s="90"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="98"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="97"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="94" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="39"/>
@@ -7284,7 +7291,7 @@
       <c r="G6" s="39"/>
       <c r="H6" s="39"/>
       <c r="I6" s="39"/>
-      <c r="J6" s="89"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="99"/>
@@ -7299,7 +7306,7 @@
       <c r="J7" s="101"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="62"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
       <c r="D8" s="42"/>
@@ -7311,7 +7318,7 @@
       <c r="J8" s="102"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="62"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="42"/>
       <c r="C9" s="42"/>
       <c r="D9" s="42"/>
@@ -7323,7 +7330,7 @@
       <c r="J9" s="102"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
       <c r="D10" s="42"/>
@@ -7335,7 +7342,7 @@
       <c r="J10" s="102"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="62"/>
+      <c r="A11" s="67"/>
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="D11" s="42"/>
@@ -7347,7 +7354,7 @@
       <c r="J11" s="102"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
       <c r="D12" s="42"/>
@@ -7359,7 +7366,7 @@
       <c r="J12" s="102"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="62"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="42"/>
       <c r="C13" s="42"/>
       <c r="D13" s="42"/>
@@ -7371,7 +7378,7 @@
       <c r="J13" s="102"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="96" t="s">
+      <c r="A14" s="94" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="39"/>
@@ -7382,15 +7389,15 @@
       <c r="G14" s="39"/>
       <c r="H14" s="39"/>
       <c r="I14" s="39"/>
-      <c r="J14" s="89"/>
+      <c r="J14" s="98"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="94" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="39"/>
       <c r="C15" s="40"/>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="79" t="s">
         <v>74</v>
       </c>
       <c r="E15" s="39"/>
@@ -7405,7 +7412,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="94" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="39"/>
@@ -7426,10 +7433,10 @@
         <v>19</v>
       </c>
       <c r="I16" s="39"/>
-      <c r="J16" s="89"/>
+      <c r="J16" s="98"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="95" t="s">
         <v>76</v>
       </c>
       <c r="B17" s="39"/>
@@ -7442,82 +7449,82 @@
       <c r="G17" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="52" t="s">
+      <c r="H17" s="79" t="s">
         <v>79</v>
       </c>
       <c r="I17" s="39"/>
-      <c r="J17" s="89"/>
+      <c r="J17" s="98"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="90"/>
+      <c r="A18" s="95"/>
       <c r="B18" s="39"/>
       <c r="C18" s="40"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="52"/>
+      <c r="H18" s="79"/>
       <c r="I18" s="39"/>
-      <c r="J18" s="89"/>
+      <c r="J18" s="98"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="90"/>
+      <c r="A19" s="95"/>
       <c r="B19" s="39"/>
       <c r="C19" s="40"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="52"/>
+      <c r="H19" s="79"/>
       <c r="I19" s="39"/>
-      <c r="J19" s="89"/>
+      <c r="J19" s="98"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="90"/>
+      <c r="A20" s="95"/>
       <c r="B20" s="39"/>
       <c r="C20" s="40"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="52"/>
+      <c r="H20" s="79"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="89"/>
+      <c r="J20" s="98"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="90"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="39"/>
       <c r="C21" s="40"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="52"/>
+      <c r="H21" s="79"/>
       <c r="I21" s="39"/>
-      <c r="J21" s="89"/>
+      <c r="J21" s="98"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="90"/>
+      <c r="A22" s="95"/>
       <c r="B22" s="39"/>
       <c r="C22" s="40"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="52"/>
+      <c r="H22" s="79"/>
       <c r="I22" s="39"/>
-      <c r="J22" s="89"/>
+      <c r="J22" s="98"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="93"/>
-      <c r="B23" s="94"/>
-      <c r="C23" s="95"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
       <c r="H23" s="104"/>
-      <c r="I23" s="94"/>
+      <c r="I23" s="92"/>
       <c r="J23" s="105"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8499,11 +8506,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8520,16 +8532,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8549,81 +8556,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="77"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="47"/>
+      <c r="S1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="98"/>
+      <c r="T1" s="97"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
+      <c r="A2" s="67"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="78"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="48"/>
       <c r="H2" s="100"/>
       <c r="I2" s="100"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="78"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="48"/>
       <c r="L2" s="100"/>
       <c r="M2" s="100"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="78"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="48"/>
       <c r="T2" s="101"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
+      <c r="A3" s="67"/>
       <c r="B3" s="42"/>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="80"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="50"/>
       <c r="H3" s="42"/>
       <c r="I3" s="42"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="80"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="50"/>
       <c r="L3" s="42"/>
       <c r="M3" s="42"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="80"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="50"/>
       <c r="T3" s="102"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
@@ -8646,36 +8653,36 @@
       <c r="Q4" s="88"/>
       <c r="R4" s="87"/>
       <c r="S4" s="88"/>
-      <c r="T4" s="115"/>
+      <c r="T4" s="110"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="112" t="s">
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
-      <c r="N5" s="92"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="92"/>
-      <c r="S5" s="92"/>
-      <c r="T5" s="98"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="97"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="94" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="39"/>
@@ -8683,7 +8690,7 @@
       <c r="D6" s="39"/>
       <c r="E6" s="39"/>
       <c r="F6" s="40"/>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="79" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="39"/>
@@ -8698,10 +8705,10 @@
       <c r="Q6" s="39"/>
       <c r="R6" s="39"/>
       <c r="S6" s="39"/>
-      <c r="T6" s="89"/>
+      <c r="T6" s="98"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="94" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="39"/>
@@ -8709,7 +8716,7 @@
       <c r="D7" s="39"/>
       <c r="E7" s="39"/>
       <c r="F7" s="40"/>
-      <c r="G7" s="52" t="s">
+      <c r="G7" s="79" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="39"/>
@@ -8724,7 +8731,7 @@
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="89"/>
+      <c r="T7" s="98"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8923,7 +8930,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="94" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="40"/>
@@ -8965,33 +8972,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="106">
+      <c r="A16" s="112">
         <v>1</v>
       </c>
       <c r="B16" s="40"/>
-      <c r="C16" s="107" t="s">
+      <c r="C16" s="113" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="40"/>
-      <c r="E16" s="107" t="s">
+      <c r="E16" s="113" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="40"/>
-      <c r="G16" s="113" t="s">
+      <c r="G16" s="106" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="40"/>
-      <c r="J16" s="113" t="s">
+      <c r="J16" s="106" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="40"/>
-      <c r="L16" s="110" t="s">
+      <c r="L16" s="108" t="s">
         <v>58</v>
       </c>
       <c r="M16" s="39"/>
       <c r="N16" s="40"/>
-      <c r="O16" s="110" t="s">
+      <c r="O16" s="108" t="s">
         <v>59</v>
       </c>
       <c r="P16" s="39"/>
@@ -9007,33 +9014,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="106">
+      <c r="A17" s="112">
         <v>2</v>
       </c>
       <c r="B17" s="40"/>
-      <c r="C17" s="107" t="s">
+      <c r="C17" s="113" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="40"/>
-      <c r="E17" s="107" t="s">
+      <c r="E17" s="113" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="40"/>
-      <c r="G17" s="113" t="s">
+      <c r="G17" s="106" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="39"/>
       <c r="I17" s="40"/>
-      <c r="J17" s="113" t="s">
+      <c r="J17" s="106" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="40"/>
-      <c r="L17" s="110" t="s">
+      <c r="L17" s="108" t="s">
         <v>64</v>
       </c>
       <c r="M17" s="39"/>
       <c r="N17" s="40"/>
-      <c r="O17" s="110" t="s">
+      <c r="O17" s="108" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="39"/>
@@ -9049,23 +9056,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="106"/>
+      <c r="A18" s="112"/>
       <c r="B18" s="40"/>
-      <c r="C18" s="107"/>
+      <c r="C18" s="113"/>
       <c r="D18" s="40"/>
-      <c r="E18" s="107"/>
+      <c r="E18" s="113"/>
       <c r="F18" s="40"/>
-      <c r="G18" s="113" t="s">
+      <c r="G18" s="106" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="39"/>
       <c r="I18" s="40"/>
-      <c r="J18" s="113"/>
+      <c r="J18" s="106"/>
       <c r="K18" s="40"/>
-      <c r="L18" s="110"/>
+      <c r="L18" s="108"/>
       <c r="M18" s="39"/>
       <c r="N18" s="40"/>
-      <c r="O18" s="110"/>
+      <c r="O18" s="108"/>
       <c r="P18" s="39"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="33"/>
@@ -9079,23 +9086,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="106"/>
+      <c r="A19" s="112"/>
       <c r="B19" s="40"/>
-      <c r="C19" s="107"/>
+      <c r="C19" s="113"/>
       <c r="D19" s="40"/>
-      <c r="E19" s="107"/>
+      <c r="E19" s="113"/>
       <c r="F19" s="40"/>
-      <c r="G19" s="113" t="s">
+      <c r="G19" s="106" t="s">
         <v>70</v>
       </c>
       <c r="H19" s="39"/>
       <c r="I19" s="40"/>
-      <c r="J19" s="113"/>
+      <c r="J19" s="106"/>
       <c r="K19" s="40"/>
-      <c r="L19" s="110"/>
+      <c r="L19" s="108"/>
       <c r="M19" s="39"/>
       <c r="N19" s="40"/>
-      <c r="O19" s="110"/>
+      <c r="O19" s="108"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="33"/>
@@ -9109,21 +9116,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="106"/>
+      <c r="A20" s="112"/>
       <c r="B20" s="40"/>
-      <c r="C20" s="107"/>
+      <c r="C20" s="113"/>
       <c r="D20" s="40"/>
-      <c r="E20" s="107"/>
+      <c r="E20" s="113"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="113"/>
+      <c r="G20" s="106"/>
       <c r="H20" s="39"/>
       <c r="I20" s="40"/>
-      <c r="J20" s="113"/>
+      <c r="J20" s="106"/>
       <c r="K20" s="40"/>
-      <c r="L20" s="110"/>
+      <c r="L20" s="108"/>
       <c r="M20" s="39"/>
       <c r="N20" s="40"/>
-      <c r="O20" s="110"/>
+      <c r="O20" s="108"/>
       <c r="P20" s="39"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="33"/>
@@ -9137,21 +9144,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="106"/>
+      <c r="A21" s="112"/>
       <c r="B21" s="40"/>
-      <c r="C21" s="107"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="40"/>
-      <c r="E21" s="107"/>
+      <c r="E21" s="113"/>
       <c r="F21" s="40"/>
-      <c r="G21" s="113"/>
+      <c r="G21" s="106"/>
       <c r="H21" s="39"/>
       <c r="I21" s="40"/>
-      <c r="J21" s="113"/>
+      <c r="J21" s="106"/>
       <c r="K21" s="40"/>
-      <c r="L21" s="110"/>
+      <c r="L21" s="108"/>
       <c r="M21" s="39"/>
       <c r="N21" s="40"/>
-      <c r="O21" s="110"/>
+      <c r="O21" s="108"/>
       <c r="P21" s="39"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="33"/>
@@ -9165,21 +9172,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="106"/>
+      <c r="A22" s="112"/>
       <c r="B22" s="40"/>
-      <c r="C22" s="107"/>
+      <c r="C22" s="113"/>
       <c r="D22" s="40"/>
-      <c r="E22" s="107"/>
+      <c r="E22" s="113"/>
       <c r="F22" s="40"/>
-      <c r="G22" s="113"/>
+      <c r="G22" s="106"/>
       <c r="H22" s="39"/>
       <c r="I22" s="40"/>
-      <c r="J22" s="113"/>
+      <c r="J22" s="106"/>
       <c r="K22" s="40"/>
-      <c r="L22" s="110"/>
+      <c r="L22" s="108"/>
       <c r="M22" s="39"/>
       <c r="N22" s="40"/>
-      <c r="O22" s="110"/>
+      <c r="O22" s="108"/>
       <c r="P22" s="39"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="33"/>
@@ -9193,21 +9200,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="106"/>
+      <c r="A23" s="112"/>
       <c r="B23" s="40"/>
-      <c r="C23" s="107"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="107"/>
+      <c r="E23" s="113"/>
       <c r="F23" s="40"/>
-      <c r="G23" s="113"/>
+      <c r="G23" s="106"/>
       <c r="H23" s="39"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="113"/>
+      <c r="J23" s="106"/>
       <c r="K23" s="40"/>
-      <c r="L23" s="110"/>
+      <c r="L23" s="108"/>
       <c r="M23" s="39"/>
       <c r="N23" s="40"/>
-      <c r="O23" s="110"/>
+      <c r="O23" s="108"/>
       <c r="P23" s="39"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="33"/>
@@ -9221,21 +9228,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="106"/>
+      <c r="A24" s="112"/>
       <c r="B24" s="40"/>
-      <c r="C24" s="107"/>
+      <c r="C24" s="113"/>
       <c r="D24" s="40"/>
-      <c r="E24" s="107"/>
+      <c r="E24" s="113"/>
       <c r="F24" s="40"/>
-      <c r="G24" s="113"/>
+      <c r="G24" s="106"/>
       <c r="H24" s="39"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="113"/>
+      <c r="J24" s="106"/>
       <c r="K24" s="40"/>
-      <c r="L24" s="110"/>
+      <c r="L24" s="108"/>
       <c r="M24" s="39"/>
       <c r="N24" s="40"/>
-      <c r="O24" s="110"/>
+      <c r="O24" s="108"/>
       <c r="P24" s="39"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="33"/>
@@ -9249,21 +9256,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="106"/>
+      <c r="A25" s="112"/>
       <c r="B25" s="40"/>
-      <c r="C25" s="107"/>
+      <c r="C25" s="113"/>
       <c r="D25" s="40"/>
-      <c r="E25" s="107"/>
+      <c r="E25" s="113"/>
       <c r="F25" s="40"/>
-      <c r="G25" s="113"/>
+      <c r="G25" s="106"/>
       <c r="H25" s="39"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="113"/>
+      <c r="J25" s="106"/>
       <c r="K25" s="40"/>
-      <c r="L25" s="110"/>
+      <c r="L25" s="108"/>
       <c r="M25" s="39"/>
       <c r="N25" s="40"/>
-      <c r="O25" s="110"/>
+      <c r="O25" s="108"/>
       <c r="P25" s="39"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="33"/>
@@ -9277,21 +9284,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="106"/>
+      <c r="A26" s="112"/>
       <c r="B26" s="40"/>
-      <c r="C26" s="107"/>
+      <c r="C26" s="113"/>
       <c r="D26" s="40"/>
-      <c r="E26" s="107"/>
+      <c r="E26" s="113"/>
       <c r="F26" s="40"/>
-      <c r="G26" s="113"/>
+      <c r="G26" s="106"/>
       <c r="H26" s="39"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="113"/>
+      <c r="J26" s="106"/>
       <c r="K26" s="40"/>
-      <c r="L26" s="110"/>
+      <c r="L26" s="108"/>
       <c r="M26" s="39"/>
       <c r="N26" s="40"/>
-      <c r="O26" s="110"/>
+      <c r="O26" s="108"/>
       <c r="P26" s="39"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="33"/>
@@ -9305,21 +9312,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="106"/>
+      <c r="A27" s="112"/>
       <c r="B27" s="40"/>
-      <c r="C27" s="107"/>
+      <c r="C27" s="113"/>
       <c r="D27" s="40"/>
-      <c r="E27" s="107"/>
+      <c r="E27" s="113"/>
       <c r="F27" s="40"/>
-      <c r="G27" s="113"/>
+      <c r="G27" s="106"/>
       <c r="H27" s="39"/>
       <c r="I27" s="40"/>
-      <c r="J27" s="113"/>
+      <c r="J27" s="106"/>
       <c r="K27" s="40"/>
-      <c r="L27" s="110"/>
+      <c r="L27" s="108"/>
       <c r="M27" s="39"/>
       <c r="N27" s="40"/>
-      <c r="O27" s="110"/>
+      <c r="O27" s="108"/>
       <c r="P27" s="39"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="33"/>
@@ -9333,21 +9340,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="106"/>
+      <c r="A28" s="112"/>
       <c r="B28" s="40"/>
-      <c r="C28" s="107"/>
+      <c r="C28" s="113"/>
       <c r="D28" s="40"/>
-      <c r="E28" s="107"/>
+      <c r="E28" s="113"/>
       <c r="F28" s="40"/>
-      <c r="G28" s="113"/>
+      <c r="G28" s="106"/>
       <c r="H28" s="39"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="113"/>
+      <c r="J28" s="106"/>
       <c r="K28" s="40"/>
-      <c r="L28" s="110"/>
+      <c r="L28" s="108"/>
       <c r="M28" s="39"/>
       <c r="N28" s="40"/>
-      <c r="O28" s="110"/>
+      <c r="O28" s="108"/>
       <c r="P28" s="39"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="33"/>
@@ -9361,21 +9368,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="106"/>
+      <c r="A29" s="112"/>
       <c r="B29" s="40"/>
-      <c r="C29" s="107"/>
+      <c r="C29" s="113"/>
       <c r="D29" s="40"/>
-      <c r="E29" s="107"/>
+      <c r="E29" s="113"/>
       <c r="F29" s="40"/>
-      <c r="G29" s="113"/>
+      <c r="G29" s="106"/>
       <c r="H29" s="39"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="113"/>
+      <c r="J29" s="106"/>
       <c r="K29" s="40"/>
-      <c r="L29" s="110"/>
+      <c r="L29" s="108"/>
       <c r="M29" s="39"/>
       <c r="N29" s="40"/>
-      <c r="O29" s="110"/>
+      <c r="O29" s="108"/>
       <c r="P29" s="39"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="33"/>
@@ -9389,21 +9396,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="106"/>
+      <c r="A30" s="112"/>
       <c r="B30" s="40"/>
-      <c r="C30" s="107"/>
+      <c r="C30" s="113"/>
       <c r="D30" s="40"/>
-      <c r="E30" s="107"/>
+      <c r="E30" s="113"/>
       <c r="F30" s="40"/>
-      <c r="G30" s="113"/>
+      <c r="G30" s="106"/>
       <c r="H30" s="39"/>
       <c r="I30" s="40"/>
-      <c r="J30" s="113"/>
+      <c r="J30" s="106"/>
       <c r="K30" s="40"/>
-      <c r="L30" s="110"/>
+      <c r="L30" s="108"/>
       <c r="M30" s="39"/>
       <c r="N30" s="40"/>
-      <c r="O30" s="110"/>
+      <c r="O30" s="108"/>
       <c r="P30" s="39"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="33"/>
@@ -9417,23 +9424,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="108"/>
-      <c r="B31" s="95"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="95"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="95"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="94"/>
-      <c r="N31" s="95"/>
-      <c r="O31" s="111"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="95"/>
+      <c r="A31" s="115"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="92"/>
+      <c r="I31" s="93"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="93"/>
+      <c r="L31" s="109"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="109"/>
+      <c r="P31" s="92"/>
+      <c r="Q31" s="93"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10431,62 +10438,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10511,62 +10518,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
